--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/142.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/142.xlsx
@@ -426,13 +426,13 @@
         <v>-11.98470309452905</v>
       </c>
       <c r="E2">
-        <v>-17.41505041310332</v>
+        <v>-11.57803761312455</v>
       </c>
       <c r="F2">
-        <v>-6.281726366568289</v>
+        <v>-6.544474152143757</v>
       </c>
       <c r="G2">
-        <v>-12.44272573143034</v>
+        <v>-5.88093557563124</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.83503606224821</v>
       </c>
       <c r="E3">
-        <v>-17.58955968746291</v>
+        <v>-11.59864216985945</v>
       </c>
       <c r="F3">
-        <v>-6.234505282771703</v>
+        <v>-6.494817668182941</v>
       </c>
       <c r="G3">
-        <v>-11.83015447849761</v>
+        <v>-6.748641492140157</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.66976908551285</v>
       </c>
       <c r="E4">
-        <v>-18.66581040554787</v>
+        <v>-12.62969871734786</v>
       </c>
       <c r="F4">
-        <v>-6.011832669592572</v>
+        <v>-6.746391605862047</v>
       </c>
       <c r="G4">
-        <v>-11.59607213244682</v>
+        <v>-5.603445949570559</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.52031141919375</v>
       </c>
       <c r="E5">
-        <v>-19.56486646418669</v>
+        <v>-14.19403742092755</v>
       </c>
       <c r="F5">
-        <v>-5.856585849531708</v>
+        <v>-7.082143824829937</v>
       </c>
       <c r="G5">
-        <v>-11.95747571866874</v>
+        <v>-6.237459985394264</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.36544391243251</v>
       </c>
       <c r="E6">
-        <v>-19.90599188271049</v>
+        <v>-13.99087649152143</v>
       </c>
       <c r="F6">
-        <v>-6.167928566241304</v>
+        <v>-7.159929594871318</v>
       </c>
       <c r="G6">
-        <v>-12.66203273679895</v>
+        <v>-6.966796788741398</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.21108496269169</v>
       </c>
       <c r="E7">
-        <v>-20.93374717264731</v>
+        <v>-13.30996155430609</v>
       </c>
       <c r="F7">
-        <v>-5.925011482105155</v>
+        <v>-6.923610871282167</v>
       </c>
       <c r="G7">
-        <v>-12.49624573628644</v>
+        <v>-5.977889110269712</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.04483549223449</v>
       </c>
       <c r="E8">
-        <v>-20.79724085216009</v>
+        <v>-13.2152077641696</v>
       </c>
       <c r="F8">
-        <v>-5.610528424571545</v>
+        <v>-6.897738472190531</v>
       </c>
       <c r="G8">
-        <v>-12.07891044736223</v>
+        <v>-6.576541421347281</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.86028452067563</v>
       </c>
       <c r="E9">
-        <v>-20.86158593933508</v>
+        <v>-15.68904971592381</v>
       </c>
       <c r="F9">
-        <v>-5.655107844720604</v>
+        <v>-6.365664835493964</v>
       </c>
       <c r="G9">
-        <v>-11.90669225259322</v>
+        <v>-6.108875474922745</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.65122492847713</v>
       </c>
       <c r="E10">
-        <v>-21.74577954628074</v>
+        <v>-16.2013831512556</v>
       </c>
       <c r="F10">
-        <v>-5.61565187695786</v>
+        <v>-6.020808858769307</v>
       </c>
       <c r="G10">
-        <v>-11.54947550508115</v>
+        <v>-6.331542451168223</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.40237946376659</v>
       </c>
       <c r="E11">
-        <v>-22.34630954138592</v>
+        <v>-15.91387939345663</v>
       </c>
       <c r="F11">
-        <v>-5.612364915103552</v>
+        <v>-6.248409429627693</v>
       </c>
       <c r="G11">
-        <v>-11.32795039393836</v>
+        <v>-6.331952603863154</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.1189162320629</v>
       </c>
       <c r="E12">
-        <v>-23.03867246089264</v>
+        <v>-18.52471221241687</v>
       </c>
       <c r="F12">
-        <v>-5.755978143359499</v>
+        <v>-6.458594404209623</v>
       </c>
       <c r="G12">
-        <v>-11.17305376778165</v>
+        <v>-6.443146640069616</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.787561625727106</v>
       </c>
       <c r="E13">
-        <v>-23.66508268495166</v>
+        <v>-18.21459325542359</v>
       </c>
       <c r="F13">
-        <v>-5.466382556075597</v>
+        <v>-6.36773782491947</v>
       </c>
       <c r="G13">
-        <v>-11.00186915780386</v>
+        <v>-5.606313737213514</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.435561696350632</v>
       </c>
       <c r="E14">
-        <v>-24.17286047543174</v>
+        <v>-19.29585699423504</v>
       </c>
       <c r="F14">
-        <v>-5.20843723051786</v>
+        <v>-6.113460096037626</v>
       </c>
       <c r="G14">
-        <v>-10.80079261941953</v>
+        <v>-4.301056925752643</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.066856593328284</v>
       </c>
       <c r="E15">
-        <v>-24.2623385933493</v>
+        <v>-20.81040512610039</v>
       </c>
       <c r="F15">
-        <v>-5.236245524229839</v>
+        <v>-5.894665070670998</v>
       </c>
       <c r="G15">
-        <v>-10.62915191964497</v>
+        <v>-4.458982119408718</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.721980565521466</v>
       </c>
       <c r="E16">
-        <v>-25.33072335208293</v>
+        <v>-20.05110230381228</v>
       </c>
       <c r="F16">
-        <v>-5.004225613277517</v>
+        <v>-6.072437685516189</v>
       </c>
       <c r="G16">
-        <v>-9.912155790582911</v>
+        <v>-3.521704462174895</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.415547352269321</v>
       </c>
       <c r="E17">
-        <v>-26.20225534570314</v>
+        <v>-22.27928812607239</v>
       </c>
       <c r="F17">
-        <v>-4.92107906358892</v>
+        <v>-5.219957335988592</v>
       </c>
       <c r="G17">
-        <v>-9.998356762171085</v>
+        <v>-5.112224113570769</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.176748394870067</v>
       </c>
       <c r="E18">
-        <v>-26.99707498963341</v>
+        <v>-22.53609335857337</v>
       </c>
       <c r="F18">
-        <v>-4.661076901770031</v>
+        <v>-5.109650275897005</v>
       </c>
       <c r="G18">
-        <v>-9.072094165712317</v>
+        <v>-4.276680730787529</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.011332367932116</v>
       </c>
       <c r="E19">
-        <v>-27.10627461185437</v>
+        <v>-20.91309280269833</v>
       </c>
       <c r="F19">
-        <v>-4.27853435005501</v>
+        <v>-5.121896031212589</v>
       </c>
       <c r="G19">
-        <v>-9.086977786705958</v>
+        <v>-5.593165882424819</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.920306856824062</v>
       </c>
       <c r="E20">
-        <v>-27.52533053957617</v>
+        <v>-22.92286579509449</v>
       </c>
       <c r="F20">
-        <v>-4.195594063849709</v>
+        <v>-4.802915767049181</v>
       </c>
       <c r="G20">
-        <v>-9.096795201611817</v>
+        <v>-5.441812975552312</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.896793539345484</v>
       </c>
       <c r="E21">
-        <v>-28.68930685613773</v>
+        <v>-24.56861287591007</v>
       </c>
       <c r="F21">
-        <v>-3.996595362675185</v>
+        <v>-4.24312412868754</v>
       </c>
       <c r="G21">
-        <v>-8.620955732282702</v>
+        <v>-3.31308111420384</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.920378450615015</v>
       </c>
       <c r="E22">
-        <v>-28.09882554485556</v>
+        <v>-25.60232763764098</v>
       </c>
       <c r="F22">
-        <v>-4.023501564285516</v>
+        <v>-3.688260448005153</v>
       </c>
       <c r="G22">
-        <v>-8.692725891452438</v>
+        <v>-3.668470221307297</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.982193439435284</v>
       </c>
       <c r="E23">
-        <v>-29.18148405366138</v>
+        <v>-24.93333164401383</v>
       </c>
       <c r="F23">
-        <v>-3.610025288647753</v>
+        <v>-4.026050450783929</v>
       </c>
       <c r="G23">
-        <v>-8.779655294226806</v>
+        <v>-4.253023123343933</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.051113528943723</v>
       </c>
       <c r="E24">
-        <v>-30.14694791938568</v>
+        <v>-24.52274849116038</v>
       </c>
       <c r="F24">
-        <v>-3.591391163921778</v>
+        <v>-3.252676703121477</v>
       </c>
       <c r="G24">
-        <v>-8.622084472499152</v>
+        <v>-4.586592107077083</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.12245727421719</v>
       </c>
       <c r="E25">
-        <v>-29.58267288718591</v>
+        <v>-26.6829800324614</v>
       </c>
       <c r="F25">
-        <v>-3.452504600066205</v>
+        <v>-3.378652332637018</v>
       </c>
       <c r="G25">
-        <v>-8.695278681825686</v>
+        <v>-5.585382824885816</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.167133377443042</v>
       </c>
       <c r="E26">
-        <v>-30.17999219421966</v>
+        <v>-24.59505010716685</v>
       </c>
       <c r="F26">
-        <v>-3.191522479609804</v>
+        <v>-3.416116905163431</v>
       </c>
       <c r="G26">
-        <v>-9.270640882274316</v>
+        <v>-4.609937998472532</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.184662986948698</v>
       </c>
       <c r="E27">
-        <v>-30.12318475203044</v>
+        <v>-27.12626782459824</v>
       </c>
       <c r="F27">
-        <v>-3.22311144214816</v>
+        <v>-3.260831980202038</v>
       </c>
       <c r="G27">
-        <v>-8.946705565039696</v>
+        <v>-5.313461431811514</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.156992813953844</v>
       </c>
       <c r="E28">
-        <v>-30.66900172417494</v>
+        <v>-25.12916097400153</v>
       </c>
       <c r="F28">
-        <v>-3.210140865355125</v>
+        <v>-3.85403333265339</v>
       </c>
       <c r="G28">
-        <v>-9.391862331566442</v>
+        <v>-4.206098373822313</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.086920444633005</v>
       </c>
       <c r="E29">
-        <v>-29.52270457013934</v>
+        <v>-25.82543196657688</v>
       </c>
       <c r="F29">
-        <v>-3.485535750252835</v>
+        <v>-3.281798787534297</v>
       </c>
       <c r="G29">
-        <v>-9.685285569519786</v>
+        <v>-4.584777591554709</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.970057790403687</v>
       </c>
       <c r="E30">
-        <v>-30.26655171063927</v>
+        <v>-25.80334207036746</v>
       </c>
       <c r="F30">
-        <v>-3.313154150465063</v>
+        <v>-3.19262503662293</v>
       </c>
       <c r="G30">
-        <v>-9.257991773162656</v>
+        <v>-4.431997353303845</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.811668356928527</v>
       </c>
       <c r="E31">
-        <v>-30.10094541617877</v>
+        <v>-24.02193096523009</v>
       </c>
       <c r="F31">
-        <v>-3.241611371354881</v>
+        <v>-3.543180181078847</v>
       </c>
       <c r="G31">
-        <v>-9.518396078563308</v>
+        <v>-4.905021534534955</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.619770151522059</v>
       </c>
       <c r="E32">
-        <v>-29.55448087225116</v>
+        <v>-25.57554171388561</v>
       </c>
       <c r="F32">
-        <v>-3.337173491676638</v>
+        <v>-3.673442611903875</v>
       </c>
       <c r="G32">
-        <v>-9.557183398617504</v>
+        <v>-4.948891466784731</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.399517250060771</v>
       </c>
       <c r="E33">
-        <v>-29.42117165441336</v>
+        <v>-25.5561734305548</v>
       </c>
       <c r="F33">
-        <v>-3.364399443104449</v>
+        <v>-3.331519055785129</v>
       </c>
       <c r="G33">
-        <v>-9.718658874000898</v>
+        <v>-4.515826001704538</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.167858476098919</v>
       </c>
       <c r="E34">
-        <v>-28.59296357162454</v>
+        <v>-25.15290829169775</v>
       </c>
       <c r="F34">
-        <v>-3.25327809785591</v>
+        <v>-3.562820772199224</v>
       </c>
       <c r="G34">
-        <v>-9.582268337439459</v>
+        <v>-3.404975005197649</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.926066294015275</v>
       </c>
       <c r="E35">
-        <v>-28.95556754236672</v>
+        <v>-23.99222417573978</v>
       </c>
       <c r="F35">
-        <v>-3.312912267183446</v>
+        <v>-3.735036698506435</v>
       </c>
       <c r="G35">
-        <v>-9.743199130043985</v>
+        <v>-3.997927834426463</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.695792098833153</v>
       </c>
       <c r="E36">
-        <v>-28.72382288502419</v>
+        <v>-24.04151661531327</v>
       </c>
       <c r="F36">
-        <v>-3.473942748450656</v>
+        <v>-3.594037797773723</v>
       </c>
       <c r="G36">
-        <v>-9.537410757500291</v>
+        <v>-4.815073407925897</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.47563009033621</v>
       </c>
       <c r="E37">
-        <v>-28.19109773123586</v>
+        <v>-26.00066579677769</v>
       </c>
       <c r="F37">
-        <v>-3.315428847353151</v>
+        <v>-3.283484515198994</v>
       </c>
       <c r="G37">
-        <v>-9.396669321151029</v>
+        <v>-3.615888645817196</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.288263240621103</v>
       </c>
       <c r="E38">
-        <v>-27.3643478170775</v>
+        <v>-24.67140017893617</v>
       </c>
       <c r="F38">
-        <v>-3.220801125461752</v>
+        <v>-4.223378334907008</v>
       </c>
       <c r="G38">
-        <v>-9.524069310639588</v>
+        <v>-3.629190718019184</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.133357063975703</v>
       </c>
       <c r="E39">
-        <v>-27.42753814338053</v>
+        <v>-22.95711011554049</v>
       </c>
       <c r="F39">
-        <v>-3.441963624865581</v>
+        <v>-3.73955958452572</v>
       </c>
       <c r="G39">
-        <v>-8.865603611754901</v>
+        <v>-3.254970680386074</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.025799939929326</v>
       </c>
       <c r="E40">
-        <v>-27.64343767017023</v>
+        <v>-23.07828755151175</v>
       </c>
       <c r="F40">
-        <v>-3.304071101893367</v>
+        <v>-4.025126821129808</v>
       </c>
       <c r="G40">
-        <v>-8.887755138502712</v>
+        <v>-2.698567378107914</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.966048187813307</v>
       </c>
       <c r="E41">
-        <v>-26.45941379917672</v>
+        <v>-22.45846172865988</v>
       </c>
       <c r="F41">
-        <v>-3.581642936325634</v>
+        <v>-4.036152391261069</v>
       </c>
       <c r="G41">
-        <v>-9.348563331868009</v>
+        <v>-2.307777171599608</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.958393165194352</v>
       </c>
       <c r="E42">
-        <v>-25.73887924286827</v>
+        <v>-22.31833262896653</v>
       </c>
       <c r="F42">
-        <v>-3.394266229812386</v>
+        <v>-4.338475843688985</v>
       </c>
       <c r="G42">
-        <v>-8.602279019166344</v>
+        <v>-2.698938156144132</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.002414114887576</v>
       </c>
       <c r="E43">
-        <v>-25.37264343597194</v>
+        <v>-21.49512850995618</v>
       </c>
       <c r="F43">
-        <v>-3.513677876028143</v>
+        <v>-3.906180717394424</v>
       </c>
       <c r="G43">
-        <v>-8.418209052124615</v>
+        <v>-3.737769620642769</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.089189876321218</v>
       </c>
       <c r="E44">
-        <v>-25.93045180728876</v>
+        <v>-21.53968416571765</v>
       </c>
       <c r="F44">
-        <v>-3.524531974107024</v>
+        <v>-4.279153968872304</v>
       </c>
       <c r="G44">
-        <v>-8.222910744906464</v>
+        <v>-3.071809611716311</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.216318306235334</v>
       </c>
       <c r="E45">
-        <v>-25.34371101553693</v>
+        <v>-21.9599537244735</v>
       </c>
       <c r="F45">
-        <v>-3.859023417887854</v>
+        <v>-3.987677987584048</v>
       </c>
       <c r="G45">
-        <v>-8.723100159428217</v>
+        <v>-3.362269906601476</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.365064540134369</v>
       </c>
       <c r="E46">
-        <v>-24.54608824619591</v>
+        <v>-20.18525834628952</v>
       </c>
       <c r="F46">
-        <v>-3.646374878649998</v>
+        <v>-3.986215090750704</v>
       </c>
       <c r="G46">
-        <v>-8.482924584941543</v>
+        <v>-3.064938733770833</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.536382467331763</v>
       </c>
       <c r="E47">
-        <v>-24.0678089354018</v>
+        <v>-20.98771752587072</v>
       </c>
       <c r="F47">
-        <v>-3.613729747673073</v>
+        <v>-4.833700384839419</v>
       </c>
       <c r="G47">
-        <v>-8.27257531443022</v>
+        <v>-3.371250610009676</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.709545789081568</v>
       </c>
       <c r="E48">
-        <v>-23.83071162178221</v>
+        <v>-19.82533523215988</v>
       </c>
       <c r="F48">
-        <v>-3.799262508347689</v>
+        <v>-4.519652220192279</v>
       </c>
       <c r="G48">
-        <v>-7.940692878578624</v>
+        <v>-3.159487133006233</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.888183598381853</v>
       </c>
       <c r="E49">
-        <v>-23.60759823589829</v>
+        <v>-19.81050900825876</v>
       </c>
       <c r="F49">
-        <v>-3.893210140601389</v>
+        <v>-4.343525571376451</v>
       </c>
       <c r="G49">
-        <v>-8.900778306872148</v>
+        <v>-2.92591665751872</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.05634113414936</v>
       </c>
       <c r="E50">
-        <v>-23.07177107741471</v>
+        <v>-18.57512318507026</v>
       </c>
       <c r="F50">
-        <v>-3.876105182100982</v>
+        <v>-4.233095912909249</v>
       </c>
       <c r="G50">
-        <v>-8.579228437711246</v>
+        <v>-3.441088129680897</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.21874191390047</v>
       </c>
       <c r="E51">
-        <v>-22.95130008338865</v>
+        <v>-20.09655912590128</v>
       </c>
       <c r="F51">
-        <v>-3.770779095202428</v>
+        <v>-4.636015474365734</v>
       </c>
       <c r="G51">
-        <v>-8.51809928005879</v>
+        <v>-3.391111844108995</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.36843333252717</v>
       </c>
       <c r="E52">
-        <v>-22.43883079383663</v>
+        <v>-19.29611058877947</v>
       </c>
       <c r="F52">
-        <v>-3.940765884828706</v>
+        <v>-4.739324486638472</v>
       </c>
       <c r="G52">
-        <v>-8.629857686373477</v>
+        <v>-3.116617973332088</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.508844348117846</v>
       </c>
       <c r="E53">
-        <v>-21.76150240803537</v>
+        <v>-19.20345348210853</v>
       </c>
       <c r="F53">
-        <v>-3.936947111101801</v>
+        <v>-4.274146487922382</v>
       </c>
       <c r="G53">
-        <v>-8.237095465707943</v>
+        <v>-3.034295405627179</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.642940644596621</v>
       </c>
       <c r="E54">
-        <v>-21.39533452824915</v>
+        <v>-18.6970614046748</v>
       </c>
       <c r="F54">
-        <v>-3.700739802928327</v>
+        <v>-4.702906142141794</v>
       </c>
       <c r="G54">
-        <v>-8.219439212496573</v>
+        <v>-3.262455146763168</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.772433583119767</v>
       </c>
       <c r="E55">
-        <v>-20.93112518619687</v>
+        <v>-17.86961863399327</v>
       </c>
       <c r="F55">
-        <v>-3.813606518294566</v>
+        <v>-4.602414407405978</v>
       </c>
       <c r="G55">
-        <v>-9.164503208490958</v>
+        <v>-3.081653276394645</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.90886616015456</v>
       </c>
       <c r="E56">
-        <v>-21.06249168868538</v>
+        <v>-15.73221965863893</v>
       </c>
       <c r="F56">
-        <v>-4.203949805841749</v>
+        <v>-4.468172499577901</v>
       </c>
       <c r="G56">
-        <v>-8.62783645389286</v>
+        <v>-2.785158815061661</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.048525396890108</v>
       </c>
       <c r="E57">
-        <v>-20.67197420415992</v>
+        <v>-16.35348553622523</v>
       </c>
       <c r="F57">
-        <v>-3.890140211006615</v>
+        <v>-4.644115250830308</v>
       </c>
       <c r="G57">
-        <v>-8.75487550900988</v>
+        <v>-3.818746887508305</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.206878191776488</v>
       </c>
       <c r="E58">
-        <v>-19.99058377717378</v>
+        <v>-14.83173713068769</v>
       </c>
       <c r="F58">
-        <v>-3.964641918479596</v>
+        <v>-4.413380137719728</v>
       </c>
       <c r="G58">
-        <v>-9.057331949916374</v>
+        <v>-3.259442985371597</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.373487694803927</v>
       </c>
       <c r="E59">
-        <v>-19.76353967585121</v>
+        <v>-16.7768933274684</v>
       </c>
       <c r="F59">
-        <v>-4.223492649608595</v>
+        <v>-3.953035662798972</v>
       </c>
       <c r="G59">
-        <v>-9.096919888031076</v>
+        <v>-3.402730649650989</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.562345167497146</v>
       </c>
       <c r="E60">
-        <v>-19.22761289093945</v>
+        <v>-17.43636594025742</v>
       </c>
       <c r="F60">
-        <v>-3.839275139005113</v>
+        <v>-3.831281393568098</v>
       </c>
       <c r="G60">
-        <v>-9.104811225881539</v>
+        <v>-4.81682558023864</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.758533005222983</v>
       </c>
       <c r="E61">
-        <v>-19.4081857919953</v>
+        <v>-15.85040377329111</v>
       </c>
       <c r="F61">
-        <v>-4.407707477745356</v>
+        <v>-4.736624837272748</v>
       </c>
       <c r="G61">
-        <v>-9.437865057829857</v>
+        <v>-3.937379452990029</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.968597689925824</v>
       </c>
       <c r="E62">
-        <v>-18.92671390702579</v>
+        <v>-15.70544279183158</v>
       </c>
       <c r="F62">
-        <v>-4.12865038055987</v>
+        <v>-4.02708922350704</v>
       </c>
       <c r="G62">
-        <v>-9.337233273823246</v>
+        <v>-3.978046912997787</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.179286858576914</v>
       </c>
       <c r="E63">
-        <v>-18.92209033506395</v>
+        <v>-15.76294988325498</v>
       </c>
       <c r="F63">
-        <v>-4.153274429975489</v>
+        <v>-4.308778872298623</v>
       </c>
       <c r="G63">
-        <v>-9.726254901911012</v>
+        <v>-3.791919620038286</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.388973674344905</v>
       </c>
       <c r="E64">
-        <v>-18.83835432218812</v>
+        <v>-15.20059492403446</v>
       </c>
       <c r="F64">
-        <v>-3.95548514520905</v>
+        <v>-4.057166415535288</v>
       </c>
       <c r="G64">
-        <v>-10.32192458259105</v>
+        <v>-4.523484372824282</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.591919232498467</v>
       </c>
       <c r="E65">
-        <v>-18.77266427823285</v>
+        <v>-16.01977322965199</v>
       </c>
       <c r="F65">
-        <v>-4.247004201602253</v>
+        <v>-3.869196597961635</v>
       </c>
       <c r="G65">
-        <v>-10.31989678766731</v>
+        <v>-4.588977555150799</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.781715395357688</v>
       </c>
       <c r="E66">
-        <v>-19.02824682275176</v>
+        <v>-15.06864877687297</v>
       </c>
       <c r="F66">
-        <v>-4.390979426413224</v>
+        <v>-4.083723046101636</v>
       </c>
       <c r="G66">
-        <v>-10.04192482203739</v>
+        <v>-5.064209998491415</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.961958493690513</v>
       </c>
       <c r="E67">
-        <v>-18.15111310678407</v>
+        <v>-13.62217719476493</v>
       </c>
       <c r="F67">
-        <v>-4.32834573872015</v>
+        <v>-4.196911168020161</v>
       </c>
       <c r="G67">
-        <v>-10.17415148843989</v>
+        <v>-5.450370401379344</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.12070759431791</v>
       </c>
       <c r="E68">
-        <v>-18.41520918243739</v>
+        <v>-14.46671948329942</v>
       </c>
       <c r="F68">
-        <v>-4.246286835431428</v>
+        <v>-4.291744325027454</v>
       </c>
       <c r="G68">
-        <v>-10.29062172891394</v>
+        <v>-5.061995173938789</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.26956447138032</v>
       </c>
       <c r="E69">
-        <v>-17.78907066681884</v>
+        <v>-13.5206125797209</v>
       </c>
       <c r="F69">
-        <v>-4.462431085109098</v>
+        <v>-3.986818970587345</v>
       </c>
       <c r="G69">
-        <v>-9.888803336744344</v>
+        <v>-5.964196572702149</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.3943566141203</v>
       </c>
       <c r="E70">
-        <v>-17.69239227522908</v>
+        <v>-13.67083564797734</v>
       </c>
       <c r="F70">
-        <v>-4.458890642829533</v>
+        <v>-4.994499751601248</v>
       </c>
       <c r="G70">
-        <v>-10.02418981950859</v>
+        <v>-5.574528543967173</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.51188586009062</v>
       </c>
       <c r="E71">
-        <v>-18.45882291560527</v>
+        <v>-14.70896114339173</v>
       </c>
       <c r="F71">
-        <v>-4.128186494814303</v>
+        <v>-4.642159475392298</v>
       </c>
       <c r="G71">
-        <v>-9.938038066243813</v>
+        <v>-5.907785811652175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.60811606848752</v>
       </c>
       <c r="E72">
-        <v>-18.48844366408944</v>
+        <v>-14.7359236776334</v>
       </c>
       <c r="F72">
-        <v>-4.754388347858381</v>
+        <v>-4.696026550861545</v>
       </c>
       <c r="G72">
-        <v>-10.41974435972121</v>
+        <v>-6.438943395251967</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.69592075693387</v>
       </c>
       <c r="E73">
-        <v>-18.32060936041716</v>
+        <v>-14.60493756696153</v>
       </c>
       <c r="F73">
-        <v>-4.532242576347429</v>
+        <v>-4.475216935971308</v>
       </c>
       <c r="G73">
-        <v>-9.819517062295109</v>
+        <v>-4.975849983117128</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.76562454786475</v>
       </c>
       <c r="E74">
-        <v>-18.4519351066396</v>
+        <v>-13.38288809972562</v>
       </c>
       <c r="F74">
-        <v>-4.602130277386817</v>
+        <v>-4.571722566764853</v>
       </c>
       <c r="G74">
-        <v>-10.20667823775867</v>
+        <v>-6.091402970118702</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.82205220951512</v>
       </c>
       <c r="E75">
-        <v>-19.0246059296496</v>
+        <v>-14.65899396119109</v>
       </c>
       <c r="F75">
-        <v>-4.782848566716363</v>
+        <v>-4.933302452984629</v>
       </c>
       <c r="G75">
-        <v>-10.21499613441186</v>
+        <v>-5.384736126525771</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.86274989447804</v>
       </c>
       <c r="E76">
-        <v>-19.23221834900525</v>
+        <v>-14.99406933844065</v>
       </c>
       <c r="F76">
-        <v>-4.761840341013965</v>
+        <v>-5.151046280117105</v>
       </c>
       <c r="G76">
-        <v>-9.891457844985934</v>
+        <v>-5.080763761258813</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.88412563036162</v>
       </c>
       <c r="E77">
-        <v>-18.90519007006733</v>
+        <v>-16.19061444006536</v>
       </c>
       <c r="F77">
-        <v>-4.690438384362259</v>
+        <v>-5.107409542072432</v>
       </c>
       <c r="G77">
-        <v>-10.01001494237179</v>
+        <v>-4.17114023932799</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.89068414315448</v>
       </c>
       <c r="E78">
-        <v>-19.55281619485228</v>
+        <v>-16.49555735126788</v>
       </c>
       <c r="F78">
-        <v>-4.857443051338459</v>
+        <v>-5.149295939794989</v>
       </c>
       <c r="G78">
-        <v>-9.93043547589058</v>
+        <v>-4.207919451787806</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.87135149395104</v>
       </c>
       <c r="E79">
-        <v>-20.6471672235459</v>
+        <v>-15.99808183915525</v>
       </c>
       <c r="F79">
-        <v>-4.962408798416796</v>
+        <v>-5.071221483713733</v>
       </c>
       <c r="G79">
-        <v>-9.639578153196721</v>
+        <v>-5.263455615245576</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.8384932848285</v>
       </c>
       <c r="E80">
-        <v>-20.65625587087929</v>
+        <v>-16.85793036983567</v>
       </c>
       <c r="F80">
-        <v>-5.040899094934256</v>
+        <v>-5.205728469110706</v>
       </c>
       <c r="G80">
-        <v>-9.076307254194644</v>
+        <v>-4.153004927768939</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.77681397848229</v>
       </c>
       <c r="E81">
-        <v>-21.15492690012994</v>
+        <v>-17.40068609355099</v>
       </c>
       <c r="F81">
-        <v>-4.949362840190106</v>
+        <v>-5.986389364815585</v>
       </c>
       <c r="G81">
-        <v>-9.565327390528047</v>
+        <v>-4.363347635837142</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.70457318495419</v>
       </c>
       <c r="E82">
-        <v>-21.84413800172733</v>
+        <v>-18.55685984939732</v>
       </c>
       <c r="F82">
-        <v>-5.06186424553171</v>
+        <v>-5.566593474261865</v>
       </c>
       <c r="G82">
-        <v>-8.704725318695326</v>
+        <v>-4.012404583946733</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.60788038251004</v>
       </c>
       <c r="E83">
-        <v>-22.81756518899413</v>
+        <v>-18.48071808743235</v>
       </c>
       <c r="F83">
-        <v>-5.330888156734488</v>
+        <v>-5.514754242194672</v>
       </c>
       <c r="G83">
-        <v>-8.857554775269584</v>
+        <v>-5.029865452428707</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.50432640089599</v>
       </c>
       <c r="E84">
-        <v>-23.58510077702819</v>
+        <v>-19.86432992183992</v>
       </c>
       <c r="F84">
-        <v>-5.380012828822707</v>
+        <v>-5.430069414239076</v>
       </c>
       <c r="G84">
-        <v>-8.333560098334059</v>
+        <v>-3.846296023721404</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.38799252387158</v>
       </c>
       <c r="E85">
-        <v>-24.49687731915456</v>
+        <v>-20.50774456579774</v>
       </c>
       <c r="F85">
-        <v>-5.330967680005157</v>
+        <v>-5.820763101197643</v>
       </c>
       <c r="G85">
-        <v>-8.730709312224569</v>
+        <v>-3.900911956578361</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.27203939779059</v>
       </c>
       <c r="E86">
-        <v>-25.63166762073668</v>
+        <v>-22.11595059708973</v>
       </c>
       <c r="F86">
-        <v>-5.290594709527515</v>
+        <v>-5.683817402166829</v>
       </c>
       <c r="G86">
-        <v>-8.588878510317572</v>
+        <v>-3.60705559737917</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.16191282115421</v>
       </c>
       <c r="E87">
-        <v>-25.83505950231718</v>
+        <v>-23.44714987333253</v>
       </c>
       <c r="F87">
-        <v>-5.655454930662376</v>
+        <v>-5.619811109687316</v>
       </c>
       <c r="G87">
-        <v>-8.538879256194754</v>
+        <v>-4.500341917165518</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.06619684606067</v>
       </c>
       <c r="E88">
-        <v>-27.43889555619177</v>
+        <v>-24.69080016158503</v>
       </c>
       <c r="F88">
-        <v>-5.566276209546593</v>
+        <v>-6.590418307588928</v>
       </c>
       <c r="G88">
-        <v>-8.544670612247174</v>
+        <v>-3.47410378101203</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.00110201280345</v>
       </c>
       <c r="E89">
-        <v>-28.95622869957184</v>
+        <v>-25.43262760267754</v>
       </c>
       <c r="F89">
-        <v>-5.83080208575217</v>
+        <v>-6.683056290978802</v>
       </c>
       <c r="G89">
-        <v>-8.51431603160075</v>
+        <v>-4.023800266422684</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.966658372398946</v>
       </c>
       <c r="E90">
-        <v>-30.43589852463011</v>
+        <v>-27.1744190887218</v>
       </c>
       <c r="F90">
-        <v>-5.69121223797162</v>
+        <v>-6.660684986715098</v>
       </c>
       <c r="G90">
-        <v>-8.279472442148172</v>
+        <v>-3.44904837318411</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.985477935236988</v>
       </c>
       <c r="E91">
-        <v>-30.84099316698627</v>
+        <v>-29.01312444700421</v>
       </c>
       <c r="F91">
-        <v>-6.044074385644334</v>
+        <v>-6.622948709680566</v>
       </c>
       <c r="G91">
-        <v>-8.635793416174511</v>
+        <v>-4.382398408211278</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.0470352392755</v>
       </c>
       <c r="E92">
-        <v>-33.36170935319387</v>
+        <v>-30.69461250892532</v>
       </c>
       <c r="F92">
-        <v>-5.892256178263657</v>
+        <v>-6.955759396001115</v>
       </c>
       <c r="G92">
-        <v>-8.566421829964732</v>
+        <v>-5.516532952903987</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.17562776136829</v>
       </c>
       <c r="E93">
-        <v>-35.11168832024399</v>
+        <v>-33.64067920172539</v>
       </c>
       <c r="F93">
-        <v>-6.257290770736808</v>
+        <v>-7.217068307397921</v>
       </c>
       <c r="G93">
-        <v>-9.200908361692997</v>
+        <v>-4.379573276448596</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.35350248148948</v>
       </c>
       <c r="E94">
-        <v>-36.22983874408492</v>
+        <v>-34.65026851818044</v>
       </c>
       <c r="F94">
-        <v>-6.198723952807779</v>
+        <v>-7.093932735522878</v>
       </c>
       <c r="G94">
-        <v>-9.055422278968779</v>
+        <v>-4.99202640540519</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.59561847861859</v>
       </c>
       <c r="E95">
-        <v>-38.31368398582455</v>
+        <v>-37.8986063225185</v>
       </c>
       <c r="F95">
-        <v>-6.135004275449636</v>
+        <v>-7.557734401799217</v>
       </c>
       <c r="G95">
-        <v>-9.206401126583508</v>
+        <v>-6.040042009048713</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.88867777607672</v>
       </c>
       <c r="E96">
-        <v>-40.19853902271913</v>
+        <v>-39.24986673861527</v>
       </c>
       <c r="F96">
-        <v>-6.125044814165777</v>
+        <v>-7.093978709913734</v>
       </c>
       <c r="G96">
-        <v>-9.958637575194006</v>
+        <v>-5.835159253655426</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.22941759050722</v>
       </c>
       <c r="E97">
-        <v>-41.94719793959602</v>
+        <v>-41.89305097588631</v>
       </c>
       <c r="F97">
-        <v>-6.354821506191318</v>
+        <v>-7.268716600778768</v>
       </c>
       <c r="G97">
-        <v>-10.08149963526585</v>
+        <v>-5.815058490382268</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.61722316759567</v>
       </c>
       <c r="E98">
-        <v>-44.3383680698662</v>
+        <v>-44.02693359117369</v>
       </c>
       <c r="F98">
-        <v>-6.397305156811293</v>
+        <v>-7.320809727454919</v>
       </c>
       <c r="G98">
-        <v>-10.3692102664842</v>
+        <v>-6.838396026677207</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.02741270475277</v>
       </c>
       <c r="E99">
-        <v>-46.36762255744337</v>
+        <v>-46.84943860643747</v>
       </c>
       <c r="F99">
-        <v>-6.198839924244171</v>
+        <v>-7.198008816010608</v>
       </c>
       <c r="G99">
-        <v>-10.69662039735028</v>
+        <v>-6.662417552001068</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.48333497090682</v>
       </c>
       <c r="E100">
-        <v>-48.67624087079072</v>
+        <v>-47.47989275778534</v>
       </c>
       <c r="F100">
-        <v>-6.41714414192464</v>
+        <v>-7.209098998799288</v>
       </c>
       <c r="G100">
-        <v>-11.22374864087507</v>
+        <v>-7.033835426422413</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.92740249176494</v>
       </c>
       <c r="E101">
-        <v>-50.20217585054836</v>
+        <v>-51.38821489247528</v>
       </c>
       <c r="F101">
-        <v>-6.545350150672218</v>
+        <v>-7.1875316251</v>
       </c>
       <c r="G101">
-        <v>-11.51949826491406</v>
+        <v>-7.538323241187038</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.43660083596777</v>
       </c>
       <c r="E102">
-        <v>-52.48687363206869</v>
+        <v>-52.90411477383191</v>
       </c>
       <c r="F102">
-        <v>-6.539189582297598</v>
+        <v>-8.092906960949657</v>
       </c>
       <c r="G102">
-        <v>-11.77393402829808</v>
+        <v>-9.380279619461602</v>
       </c>
     </row>
   </sheetData>
